--- a/assets_management/tests/data/account_invoice.xlsx
+++ b/assets_management/tests/data/account_invoice.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -73,6 +73,24 @@
     <t xml:space="preserve">&lt;002-12-01</t>
   </si>
   <si>
+    <t xml:space="preserve">z0bug.sale_invoice_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">base.res_partner_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset #4 (20%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;001-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">out_invoice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">external.INV</t>
+  </si>
+  <si>
     <t xml:space="preserve">z0bug.sale_invoice_1</t>
   </si>
   <si>
@@ -83,12 +101,6 @@
   </si>
   <si>
     <t xml:space="preserve">####-01-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">out_invoice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">external.INV</t>
   </si>
 </sst>
 </file>
@@ -211,12 +223,118 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.97"/>
@@ -224,7 +342,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.28"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="1" width="11.53"/>
   </cols>
@@ -312,6 +430,27 @@
         <v>21</v>
       </c>
       <c r="G4" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" s="4" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>22</v>
       </c>
     </row>

--- a/assets_management/tests/data/account_invoice.xlsx
+++ b/assets_management/tests/data/account_invoice.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Asset 20-010-001</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;002-10-01</t>
+    <t xml:space="preserve">&lt;003-10-01</t>
   </si>
   <si>
     <t xml:space="preserve">in_invoice</t>
@@ -70,7 +70,7 @@
     <t xml:space="preserve">Asset 20-012-001</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;002-12-01</t>
+    <t xml:space="preserve">&lt;003-12-01</t>
   </si>
   <si>
     <t xml:space="preserve">z0bug.sale_invoice_4</t>
@@ -82,7 +82,7 @@
     <t xml:space="preserve">Asset #4 (20%)</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;001-07-31</t>
+    <t xml:space="preserve">&lt;002-07-31</t>
   </si>
   <si>
     <t xml:space="preserve">out_invoice</t>

--- a/assets_management/tests/data/account_invoice.xlsx
+++ b/assets_management/tests/data/account_invoice.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -91,16 +91,28 @@
     <t xml:space="preserve">external.INV</t>
   </si>
   <si>
-    <t xml:space="preserve">z0bug.sale_invoice_1</t>
+    <t xml:space="preserve">z0bug.sale_invoice_2</t>
   </si>
   <si>
     <t xml:space="preserve">base.res_partner_18</t>
   </si>
   <si>
-    <t xml:space="preserve">Asset #1 and #2</t>
+    <t xml:space="preserve">Asset #2</t>
   </si>
   <si>
     <t xml:space="preserve">####-01-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z0bug.sale_invoice_13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">base.res_partner_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset #1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">####-01-15</t>
   </si>
 </sst>
 </file>
@@ -334,7 +346,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.97"/>
@@ -454,6 +466,27 @@
         <v>22</v>
       </c>
     </row>
+    <row r="6" s="4" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
